--- a/结果/Q2_结果.xlsx
+++ b/结果/Q2_结果.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q2_运输架次" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q2_逐箱交付" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源使用" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可行性检验" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="权衡分析" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Q2_运输架次" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Q2_逐箱交付" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="资源使用" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="可行性检验" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="权衡分析" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -508,14 +508,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>O01→S001→O01</t>
+          <t>O01→S011→O01</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1252.5</v>
+        <v>1220.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2861</v>
+        <v>1.1937</v>
       </c>
       <c r="I2" t="n">
         <v>22</v>
@@ -524,10 +524,10 @@
         <v>0.055</v>
       </c>
       <c r="K2" t="n">
-        <v>71.42</v>
+        <v>73.47</v>
       </c>
       <c r="L2" t="n">
-        <v>2124</v>
+        <v>2065.4</v>
       </c>
     </row>
     <row r="3">
@@ -556,14 +556,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>O01→S005→S004→O01</t>
+          <t>O01→S013→O01</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2421</v>
+        <v>1612.1</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2199</v>
+        <v>2.0253</v>
       </c>
       <c r="I3" t="n">
         <v>22</v>
@@ -572,10 +572,10 @@
         <v>0.055</v>
       </c>
       <c r="K3" t="n">
-        <v>28.45</v>
+        <v>54.99</v>
       </c>
       <c r="L3" t="n">
-        <v>3851.2</v>
+        <v>2697.2</v>
       </c>
     </row>
     <row r="4">
@@ -604,26 +604,26 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>O01→S001→S013→O01</t>
+          <t>O01→S006→O01</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1964.5</v>
+        <v>1312.6</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1575</v>
+        <v>1.3096</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J4" t="n">
-        <v>0.051</v>
+        <v>0.039</v>
       </c>
       <c r="K4" t="n">
-        <v>52.05</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>3087.8</v>
+        <v>2190.9</v>
       </c>
     </row>
     <row r="5">
@@ -652,26 +652,26 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>O01→S001→O01</t>
+          <t>O01→S009→S002→S013→O01</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1252.5</v>
+        <v>2678.9</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2861</v>
+        <v>3.3978</v>
       </c>
       <c r="I5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>0.055</v>
+        <v>0.051</v>
       </c>
       <c r="K5" t="n">
-        <v>71.42</v>
+        <v>24.49</v>
       </c>
       <c r="L5" t="n">
-        <v>2124</v>
+        <v>4160.5</v>
       </c>
     </row>
     <row r="6">
@@ -700,14 +700,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>O01→S014→O01</t>
+          <t>O01→S012→O01</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1868.6</v>
+        <v>1923.9</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1373</v>
+        <v>2.7555</v>
       </c>
       <c r="I6" t="n">
         <v>25</v>
@@ -716,10 +716,10 @@
         <v>0.067</v>
       </c>
       <c r="K6" t="n">
-        <v>46.57</v>
+        <v>31.11</v>
       </c>
       <c r="L6" t="n">
-        <v>3461.4</v>
+        <v>3784.6</v>
       </c>
     </row>
     <row r="7">
@@ -748,14 +748,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>O01→S010→O01</t>
+          <t>O01→S014→O01</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1554.6</v>
+        <v>1868.6</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8211</v>
+        <v>2.1373</v>
       </c>
       <c r="I7" t="n">
         <v>25</v>
@@ -764,10 +764,10 @@
         <v>0.067</v>
       </c>
       <c r="K7" t="n">
-        <v>54.47</v>
+        <v>46.57</v>
       </c>
       <c r="L7" t="n">
-        <v>3010.4</v>
+        <v>3461.4</v>
       </c>
     </row>
     <row r="8">
@@ -796,26 +796,26 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>O01→S002→O01</t>
+          <t>O01→S001→O01</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2111</v>
+        <v>1627.4</v>
       </c>
       <c r="H8" t="n">
-        <v>5.8718</v>
+        <v>3.0047</v>
       </c>
       <c r="I8" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="J8" t="n">
-        <v>0.156</v>
+        <v>0.188</v>
       </c>
       <c r="K8" t="n">
-        <v>26.6</v>
+        <v>62.44</v>
       </c>
       <c r="L8" t="n">
-        <v>4534.7</v>
+        <v>3274.5</v>
       </c>
     </row>
     <row r="9">
@@ -844,26 +844,26 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>O01→S001→S006→O01</t>
+          <t>O01→S001→O01</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2257.3</v>
+        <v>1561.4</v>
       </c>
       <c r="H9" t="n">
-        <v>5.12</v>
+        <v>2.9263</v>
       </c>
       <c r="I9" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J9" t="n">
-        <v>0.182</v>
+        <v>0.206</v>
       </c>
       <c r="K9" t="n">
-        <v>36</v>
+        <v>63.42</v>
       </c>
       <c r="L9" t="n">
-        <v>4477.3</v>
+        <v>3187.3</v>
       </c>
     </row>
     <row r="10">
@@ -888,18 +888,18 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1252.5</v>
+        <v>1220.6</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>O01→S002→O01</t>
+          <t>O01→S006→O01</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3260.3</v>
+        <v>2533.2</v>
       </c>
       <c r="H10" t="n">
-        <v>3.0283</v>
+        <v>1.355</v>
       </c>
       <c r="I10" t="n">
         <v>22</v>
@@ -908,10 +908,10 @@
         <v>0.055</v>
       </c>
       <c r="K10" t="n">
-        <v>32.71</v>
+        <v>69.89</v>
       </c>
       <c r="L10" t="n">
-        <v>4635.1</v>
+        <v>3424.6</v>
       </c>
     </row>
     <row r="11">
@@ -922,7 +922,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U04</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -936,18 +936,18 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1252.5</v>
+        <v>1312.6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>O01→S013→O01</t>
+          <t>O01→S005→O01</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2864.6</v>
+        <v>3008.4</v>
       </c>
       <c r="H11" t="n">
-        <v>2.0253</v>
+        <v>2.2015</v>
       </c>
       <c r="I11" t="n">
         <v>22</v>
@@ -956,10 +956,10 @@
         <v>0.055</v>
       </c>
       <c r="K11" t="n">
-        <v>54.99</v>
+        <v>51.08</v>
       </c>
       <c r="L11" t="n">
-        <v>3949.7</v>
+        <v>4144.3</v>
       </c>
     </row>
     <row r="12">
@@ -970,44 +970,44 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B-B03</t>
+          <t>C-B03</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1554.6</v>
+        <v>1561.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>O01→S012→O01</t>
+          <t>O01→S006→S007→O01</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3478.5</v>
+        <v>3975.2</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7555</v>
+        <v>4.2979</v>
       </c>
       <c r="I12" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="J12" t="n">
-        <v>0.067</v>
+        <v>0.191</v>
       </c>
       <c r="K12" t="n">
-        <v>31.11</v>
+        <v>46.28</v>
       </c>
       <c r="L12" t="n">
-        <v>5339.2</v>
+        <v>5972.6</v>
       </c>
     </row>
     <row r="13">
@@ -1018,44 +1018,44 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B-B04</t>
+          <t>C-B04</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1868.6</v>
+        <v>1627.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>O01→S008→O01</t>
+          <t>O01→S002→O01</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3774.5</v>
+        <v>3804.5</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7735</v>
+        <v>6.301</v>
       </c>
       <c r="I13" t="n">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="J13" t="n">
-        <v>0.062</v>
+        <v>0.184</v>
       </c>
       <c r="K13" t="n">
-        <v>30.66</v>
+        <v>21.24</v>
       </c>
       <c r="L13" t="n">
-        <v>5643</v>
+        <v>6344.3</v>
       </c>
     </row>
     <row r="14">
@@ -1066,44 +1066,44 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C-B03</t>
+          <t>B-B03</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2111</v>
+        <v>1868.6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>O01→S007→S003→O01</t>
+          <t>O01→S010→O01</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4672.4</v>
+        <v>3423.2</v>
       </c>
       <c r="H14" t="n">
-        <v>5.5676</v>
+        <v>1.8211</v>
       </c>
       <c r="I14" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>0.12</v>
+        <v>0.067</v>
       </c>
       <c r="K14" t="n">
-        <v>30.4</v>
+        <v>54.47</v>
       </c>
       <c r="L14" t="n">
-        <v>7013.7</v>
+        <v>4879</v>
       </c>
     </row>
     <row r="15">
@@ -1114,44 +1114,44 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U03</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>A-B01</t>
+          <t>B-B04</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2124</v>
+        <v>1923.9</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>O01→S006→O01</t>
+          <t>O01→S004→O01</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>3436.6</v>
+        <v>3849.7</v>
       </c>
       <c r="H15" t="n">
-        <v>1.355</v>
+        <v>3.047</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>0.055</v>
+        <v>0.054</v>
       </c>
       <c r="K15" t="n">
-        <v>69.89</v>
+        <v>23.83</v>
       </c>
       <c r="L15" t="n">
-        <v>4328.1</v>
+        <v>5836.7</v>
       </c>
     </row>
     <row r="16">
@@ -1162,44 +1162,44 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C-B04</t>
+          <t>A-B01</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2257.3</v>
+        <v>2065.4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>O01→S001→S005→O01</t>
+          <t>O01→S009→O01</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>4632.8</v>
+        <v>3757</v>
       </c>
       <c r="H16" t="n">
-        <v>4.5861</v>
+        <v>2.3383</v>
       </c>
       <c r="I16" t="n">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>0.238</v>
+        <v>0.055</v>
       </c>
       <c r="K16" t="n">
-        <v>42.67</v>
+        <v>48.04</v>
       </c>
       <c r="L16" t="n">
-        <v>6708.2</v>
+        <v>4932.5</v>
       </c>
     </row>
     <row r="17">
@@ -1210,44 +1210,44 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B-B02</t>
+          <t>A-B03</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3478.5</v>
+        <v>2533.2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>O01→S008→O01</t>
+          <t>O01→S015→S003→O01</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>5444.4</v>
+        <v>5077.1</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9861</v>
+        <v>3.3367</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>0.067</v>
+        <v>0.055</v>
       </c>
       <c r="K17" t="n">
-        <v>25.35</v>
+        <v>25.85</v>
       </c>
       <c r="L17" t="n">
-        <v>7405</v>
+        <v>6541.1</v>
       </c>
     </row>
     <row r="18">
@@ -1258,44 +1258,44 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B-B01</t>
+          <t>A-B02</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3774.5</v>
+        <v>2697.2</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>O01→S015→O01</t>
+          <t>O01→S011→S015→O01</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>5604.1</v>
+        <v>4970.7</v>
       </c>
       <c r="H18" t="n">
-        <v>2.311</v>
+        <v>2.5833</v>
       </c>
       <c r="I18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>0.067</v>
+        <v>0.051</v>
       </c>
       <c r="K18" t="n">
-        <v>42.22</v>
+        <v>42.59</v>
       </c>
       <c r="L18" t="n">
-        <v>7272.2</v>
+        <v>6217</v>
       </c>
     </row>
     <row r="19">
@@ -1306,44 +1306,44 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C-B02</t>
+          <t>B-B02</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4632.8</v>
+        <v>3461.4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>O01→S007→S003→O01</t>
+          <t>O01→S008→O01</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>7392.2</v>
+        <v>5427.3</v>
       </c>
       <c r="H19" t="n">
-        <v>6.082</v>
+        <v>2.9861</v>
       </c>
       <c r="I19" t="n">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>0.22</v>
+        <v>0.067</v>
       </c>
       <c r="K19" t="n">
-        <v>23.97</v>
+        <v>25.35</v>
       </c>
       <c r="L19" t="n">
-        <v>9872.700000000001</v>
+        <v>7387.9</v>
       </c>
     </row>
     <row r="20">
@@ -1364,34 +1364,34 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>C-B01</t>
+          <t>C-B02</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4672.4</v>
+        <v>3804.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>O01→S011→S004→O01</t>
+          <t>O01→S005→S004→O01</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>7362.3</v>
+        <v>6522.3</v>
       </c>
       <c r="H20" t="n">
-        <v>6.2895</v>
+        <v>6.3448</v>
       </c>
       <c r="I20" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J20" t="n">
-        <v>0.196</v>
+        <v>0.203</v>
       </c>
       <c r="K20" t="n">
-        <v>21.38</v>
+        <v>20.69</v>
       </c>
       <c r="L20" t="n">
-        <v>9899</v>
+        <v>9074</v>
       </c>
     </row>
     <row r="21">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1412,34 +1412,34 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B-B03</t>
+          <t>B-B01</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5444.4</v>
+        <v>3849.7</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>O01→S005→O01</t>
+          <t>O01→S008→O01</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>6963.4</v>
+        <v>5755.6</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0942</v>
+        <v>2.7735</v>
       </c>
       <c r="I21" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>0.054</v>
+        <v>0.062</v>
       </c>
       <c r="K21" t="n">
-        <v>47.65</v>
+        <v>30.66</v>
       </c>
       <c r="L21" t="n">
-        <v>8537.6</v>
+        <v>7624.1</v>
       </c>
     </row>
     <row r="22">
@@ -1450,44 +1450,44 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>B-B04</t>
+          <t>C-B01</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5643</v>
+        <v>3975.2</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>O01→S009→O01</t>
+          <t>O01→S003→O01</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>7203.8</v>
+        <v>6477.1</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1025</v>
+        <v>6.3228</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="J22" t="n">
-        <v>0.067</v>
+        <v>0.184</v>
       </c>
       <c r="K22" t="n">
-        <v>47.44</v>
+        <v>20.96</v>
       </c>
       <c r="L22" t="n">
-        <v>8781.6</v>
+        <v>9022.9</v>
       </c>
     </row>
   </sheetData>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Q2-T01</t>
+          <t>Q2-T07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>909.4</v>
+        <v>1314.9</v>
       </c>
       <c r="E2" t="n">
         <v>7200</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Q2-T15</t>
+          <t>Q2-T07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3530.2</v>
+        <v>1314.9</v>
       </c>
       <c r="E3" t="n">
         <v>7200</v>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Q2-T04</t>
+          <t>Q2-T08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>909.4</v>
+        <v>1248.9</v>
       </c>
       <c r="E4" t="n">
         <v>7200</v>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Q2-T15</t>
+          <t>Q2-T08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3530.2</v>
+        <v>1248.9</v>
       </c>
       <c r="E5" t="n">
         <v>10800</v>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Q2-T15</t>
+          <t>Q2-T08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3530.2</v>
+        <v>1248.9</v>
       </c>
       <c r="E6" t="n">
         <v>10800</v>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Q2-T03</t>
+          <t>Q2-T07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>939.4</v>
+        <v>1314.9</v>
       </c>
       <c r="E7" t="n">
         <v>3600</v>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Q2-T15</t>
+          <t>Q2-T07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3530.2</v>
+        <v>1314.9</v>
       </c>
       <c r="E8" t="n">
         <v>3600</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Q2-T08</t>
+          <t>Q2-T07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1104.9</v>
+        <v>1314.9</v>
       </c>
       <c r="E9" t="n">
         <v>3600</v>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1104.9</v>
+        <v>1248.9</v>
       </c>
       <c r="E10" t="n">
         <v>3600</v>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Q2-T04</t>
+          <t>Q2-T08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>909.4</v>
+        <v>1248.9</v>
       </c>
       <c r="E11" t="n">
         <v>3600</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Q2-T15</t>
+          <t>Q2-T07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3530.2</v>
+        <v>1314.9</v>
       </c>
       <c r="E12" t="n">
         <v>3600</v>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1104.9</v>
+        <v>1248.9</v>
       </c>
       <c r="E13" t="n">
         <v>3600</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Q2-T03</t>
+          <t>Q2-T07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>939.4</v>
+        <v>1314.9</v>
       </c>
       <c r="E14" t="n">
         <v>3600</v>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Q2-T15</t>
+          <t>Q2-T07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3530.2</v>
+        <v>1314.9</v>
       </c>
       <c r="E15" t="n">
         <v>3600</v>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Q2-T01</t>
+          <t>Q2-T08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>909.4</v>
+        <v>1248.9</v>
       </c>
       <c r="E16" t="n">
         <v>3600</v>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Q2-T07</t>
+          <t>Q2-T12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1488.9</v>
+        <v>3182.4</v>
       </c>
       <c r="E17" t="n">
         <v>7200</v>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Q2-T09</t>
+          <t>Q2-T12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2538.3</v>
+        <v>3182.4</v>
       </c>
       <c r="E18" t="n">
         <v>7200</v>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Q2-T07</t>
+          <t>Q2-T12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1488.9</v>
+        <v>3182.4</v>
       </c>
       <c r="E19" t="n">
         <v>10800</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Q2-T07</t>
+          <t>Q2-T12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1488.9</v>
+        <v>3182.4</v>
       </c>
       <c r="E20" t="n">
         <v>3600</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Q2-T07</t>
+          <t>Q2-T12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1488.9</v>
+        <v>3182.4</v>
       </c>
       <c r="E21" t="n">
         <v>3600</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Q2-T09</t>
+          <t>Q2-T04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2538.3</v>
+        <v>1527.9</v>
       </c>
       <c r="E22" t="n">
         <v>3600</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Q2-T07</t>
+          <t>Q2-T12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1488.9</v>
+        <v>3182.4</v>
       </c>
       <c r="E23" t="n">
         <v>3600</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Q2-T07</t>
+          <t>Q2-T12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1488.9</v>
+        <v>3182.4</v>
       </c>
       <c r="E24" t="n">
         <v>3600</v>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Q2-T18</t>
+          <t>Q2-T21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6601.7</v>
+        <v>5686.6</v>
       </c>
       <c r="E25" t="n">
         <v>10800</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Q2-T18</t>
+          <t>Q2-T21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6601.7</v>
+        <v>5686.6</v>
       </c>
       <c r="E26" t="n">
         <v>10800</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Q2-T18</t>
+          <t>Q2-T21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6601.7</v>
+        <v>5686.6</v>
       </c>
       <c r="E27" t="n">
         <v>14400</v>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Q2-T18</t>
+          <t>Q2-T21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6601.7</v>
+        <v>5686.6</v>
       </c>
       <c r="E28" t="n">
         <v>7200</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Q2-T13</t>
+          <t>Q2-T21</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3882</v>
+        <v>5686.6</v>
       </c>
       <c r="E29" t="n">
         <v>7200</v>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Q2-T18</t>
+          <t>Q2-T21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6601.7</v>
+        <v>5686.6</v>
       </c>
       <c r="E30" t="n">
         <v>7200</v>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Q2-T18</t>
+          <t>Q2-T16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6601.7</v>
+        <v>4223.9</v>
       </c>
       <c r="E31" t="n">
         <v>7200</v>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Q2-T13</t>
+          <t>Q2-T21</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3882</v>
+        <v>5686.6</v>
       </c>
       <c r="E32" t="n">
         <v>7200</v>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6642.7</v>
+        <v>5802.7</v>
       </c>
       <c r="E33" t="n">
         <v>10800</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6642.7</v>
+        <v>5802.7</v>
       </c>
       <c r="E34" t="n">
         <v>14400</v>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6642.7</v>
+        <v>5802.7</v>
       </c>
       <c r="E35" t="n">
         <v>7200</v>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Q2-T02</t>
+          <t>Q2-T19</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1610.6</v>
+        <v>5802.7</v>
       </c>
       <c r="E36" t="n">
         <v>7200</v>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Q2-T19</t>
+          <t>Q2-T14</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6642.7</v>
+        <v>3168.4</v>
       </c>
       <c r="E37" t="n">
         <v>7200</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Q2-T19</t>
+          <t>Q2-T14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6642.7</v>
+        <v>3168.4</v>
       </c>
       <c r="E38" t="n">
         <v>7200</v>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Q2-T02</t>
+          <t>Q2-T10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1100.6</v>
+        <v>2443.2</v>
       </c>
       <c r="E39" t="n">
         <v>14400</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Q2-T15</t>
+          <t>Q2-T19</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4127.4</v>
+        <v>5167.1</v>
       </c>
       <c r="E40" t="n">
         <v>18000</v>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Q2-T15</t>
+          <t>Q2-T19</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4127.4</v>
+        <v>5167.1</v>
       </c>
       <c r="E41" t="n">
         <v>10800</v>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Q2-T20</t>
+          <t>Q2-T19</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>6486.7</v>
+        <v>5167.1</v>
       </c>
       <c r="E42" t="n">
         <v>10800</v>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Q2-T20</t>
+          <t>Q2-T19</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>6486.7</v>
+        <v>5167.1</v>
       </c>
       <c r="E43" t="n">
         <v>10800</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Q2-T15</t>
+          <t>Q2-T10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4127.4</v>
+        <v>2443.2</v>
       </c>
       <c r="E44" t="n">
         <v>10800</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Q2-T14</t>
+          <t>Q2-T09</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3059.1</v>
+        <v>2155.7</v>
       </c>
       <c r="E45" t="n">
         <v>7200</v>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Q2-T08</t>
+          <t>Q2-T11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1905.6</v>
+        <v>2656.5</v>
       </c>
       <c r="E46" t="n">
         <v>10800</v>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Q2-T08</t>
+          <t>Q2-T03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1905.6</v>
+        <v>935.1</v>
       </c>
       <c r="E47" t="n">
         <v>3600</v>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Q2-T08</t>
+          <t>Q2-T09</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1905.6</v>
+        <v>2155.7</v>
       </c>
       <c r="E48" t="n">
         <v>3600</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Q2-T14</t>
+          <t>Q2-T11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3059.1</v>
+        <v>2656.5</v>
       </c>
       <c r="E49" t="n">
         <v>3600</v>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Q2-T08</t>
+          <t>Q2-T03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1905.6</v>
+        <v>935.1</v>
       </c>
       <c r="E50" t="n">
         <v>3600</v>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Q2-T18</t>
+          <t>Q2-T11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5962.5</v>
+        <v>3415.4</v>
       </c>
       <c r="E51" t="n">
         <v>7200</v>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Q2-T18</t>
+          <t>Q2-T11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>5962.5</v>
+        <v>3415.4</v>
       </c>
       <c r="E52" t="n">
         <v>10800</v>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Q2-T13</t>
+          <t>Q2-T11</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3221,7 +3221,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3386.8</v>
+        <v>3415.4</v>
       </c>
       <c r="E53" t="n">
         <v>3600</v>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Q2-T13</t>
+          <t>Q2-T11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3386.8</v>
+        <v>3415.4</v>
       </c>
       <c r="E54" t="n">
         <v>3600</v>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Q2-T13</t>
+          <t>Q2-T11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3386.8</v>
+        <v>3415.4</v>
       </c>
       <c r="E55" t="n">
         <v>3600</v>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Q2-T16</t>
+          <t>Q2-T18</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4771.7</v>
+        <v>4754.6</v>
       </c>
       <c r="E56" t="n">
         <v>10800</v>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Q2-T12</t>
+          <t>Q2-T20</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3101.8</v>
+        <v>5082.8</v>
       </c>
       <c r="E57" t="n">
         <v>14400</v>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Q2-T16</t>
+          <t>Q2-T18</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4771.7</v>
+        <v>4754.6</v>
       </c>
       <c r="E58" t="n">
         <v>7200</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Q2-T16</t>
+          <t>Q2-T18</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4771.7</v>
+        <v>4754.6</v>
       </c>
       <c r="E59" t="n">
         <v>7200</v>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Q2-T12</t>
+          <t>Q2-T20</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3101.8</v>
+        <v>5082.8</v>
       </c>
       <c r="E60" t="n">
         <v>7200</v>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Q2-T21</t>
+          <t>Q2-T15</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>6735</v>
+        <v>3192.8</v>
       </c>
       <c r="E61" t="n">
         <v>14400</v>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Q2-T21</t>
+          <t>Q2-T04</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>6735</v>
+        <v>1127.4</v>
       </c>
       <c r="E62" t="n">
         <v>10800</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Q2-T21</t>
+          <t>Q2-T15</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>6735</v>
+        <v>3192.8</v>
       </c>
       <c r="E63" t="n">
         <v>10800</v>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Q2-T06</t>
+          <t>Q2-T13</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1084.8</v>
+        <v>2953.4</v>
       </c>
       <c r="E64" t="n">
         <v>7200</v>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Q2-T06</t>
+          <t>Q2-T13</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1084.8</v>
+        <v>2953.4</v>
       </c>
       <c r="E65" t="n">
         <v>3600</v>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Q2-T06</t>
+          <t>Q2-T13</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1084.8</v>
+        <v>2953.4</v>
       </c>
       <c r="E66" t="n">
         <v>3600</v>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Q2-T19</t>
+          <t>Q2-T01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>5795.1</v>
+        <v>892.5</v>
       </c>
       <c r="E67" t="n">
         <v>14400</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Q2-T19</t>
+          <t>Q2-T17</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>5795.1</v>
+        <v>3589.7</v>
       </c>
       <c r="E68" t="n">
         <v>10800</v>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Q2-T19</t>
+          <t>Q2-T01</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5795.1</v>
+        <v>892.5</v>
       </c>
       <c r="E69" t="n">
         <v>10800</v>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Q2-T11</t>
+          <t>Q2-T05</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2826.5</v>
+        <v>1271.9</v>
       </c>
       <c r="E70" t="n">
         <v>7200</v>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Q2-T11</t>
+          <t>Q2-T05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2826.5</v>
+        <v>1271.9</v>
       </c>
       <c r="E71" t="n">
         <v>7200</v>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Q2-T11</t>
+          <t>Q2-T05</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2826.5</v>
+        <v>1271.9</v>
       </c>
       <c r="E72" t="n">
         <v>3600</v>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Q2-T10</t>
+          <t>Q2-T02</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3885,7 +3885,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2336</v>
+        <v>1083.6</v>
       </c>
       <c r="E73" t="n">
         <v>7200</v>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Q2-T03</t>
+          <t>Q2-T04</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1436</v>
+        <v>2150.4</v>
       </c>
       <c r="E74" t="n">
         <v>3600</v>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Q2-T10</t>
+          <t>Q2-T02</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3951,7 +3951,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2336</v>
+        <v>1083.6</v>
       </c>
       <c r="E75" t="n">
         <v>3600</v>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Q2-T05</t>
+          <t>Q2-T06</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Q2-T05</t>
+          <t>Q2-T06</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Q2-T05</t>
+          <t>Q2-T06</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Q2-T17</t>
+          <t>Q2-T16</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>4992.7</v>
+        <v>3761.8</v>
       </c>
       <c r="E79" t="n">
         <v>14400</v>
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>4992.7</v>
+        <v>4259</v>
       </c>
       <c r="E80" t="n">
         <v>7200</v>
@@ -4151,7 +4151,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>4992.7</v>
+        <v>4259</v>
       </c>
       <c r="E81" t="n">
         <v>10800</v>
@@ -4226,14 +4226,14 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3260.3</v>
+        <v>5077.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Q2-T01,Q2-T09</t>
+          <t>Q2-T01,Q2-T09,Q2-T16</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -4250,14 +4250,14 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2421</v>
+        <v>3303.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Q2-T02</t>
+          <t>Q2-T02,Q2-T15</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -4277,11 +4277,11 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3277.2</v>
+        <v>3008.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Q2-T03,Q2-T14</t>
+          <t>Q2-T03,Q2-T10</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -4301,11 +4301,11 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2864.6</v>
+        <v>4952.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Q2-T04,Q2-T10</t>
+          <t>Q2-T04,Q2-T17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -4322,14 +4322,14 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>7164.9</v>
+        <v>5755.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Q2-T05,Q2-T12,Q2-T17,Q2-T21</t>
+          <t>Q2-T05,Q2-T14,Q2-T20</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -4346,14 +4346,14 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>6963.4</v>
+        <v>5389.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Q2-T06,Q2-T11,Q2-T16,Q2-T20</t>
+          <t>Q2-T06,Q2-T13,Q2-T18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -4373,11 +4373,11 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>7362.3</v>
+        <v>6522.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Q2-T07,Q2-T13,Q2-T19</t>
+          <t>Q2-T07,Q2-T12,Q2-T19</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -4397,11 +4397,11 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>7392.2</v>
+        <v>6477.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Q2-T08,Q2-T15,Q2-T18</t>
+          <t>Q2-T08,Q2-T11,Q2-T21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -4421,15 +4421,15 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>2565.1</v>
+        <v>2912.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Q2-T01,Q2-T14</t>
+          <t>Q2-T01,Q2-T15</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1763</v>
+        <v>2020.4</v>
       </c>
     </row>
     <row r="11">
@@ -4444,18 +4444,18 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>2421</v>
+        <v>3885.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Q2-T02</t>
+          <t>Q2-T02,Q2-T17</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1430.2</v>
+        <v>2331.4</v>
       </c>
     </row>
     <row r="12">
@@ -4470,18 +4470,18 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>1964.5</v>
+        <v>3856.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Q2-T03</t>
+          <t>Q2-T03,Q2-T16</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1123.3</v>
+        <v>2342.3</v>
       </c>
     </row>
     <row r="13">
@@ -4499,7 +4499,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1252.5</v>
+        <v>2678.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>871.5</v>
+        <v>1481.6</v>
       </c>
     </row>
     <row r="14">
@@ -4525,7 +4525,7 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2007.8</v>
+        <v>1312.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1374.8</v>
+        <v>891.4</v>
       </c>
     </row>
     <row r="15">
@@ -4551,7 +4551,7 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1612.1</v>
+        <v>1695.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1085.1</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="16">
@@ -4577,15 +4577,15 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>3698.2</v>
+        <v>3829.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Q2-T05,Q2-T17</t>
+          <t>Q2-T05,Q2-T20</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3260.9</v>
+        <v>3729.2</v>
       </c>
     </row>
     <row r="17">
@@ -4603,15 +4603,15 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>3520.5</v>
+        <v>3834.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Q2-T06,Q2-T16</t>
+          <t>Q2-T06,Q2-T18</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3416.4</v>
+        <v>3553.4</v>
       </c>
     </row>
     <row r="18">
@@ -4626,18 +4626,18 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3442.9</v>
+        <v>1554.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Q2-T11,Q2-T20</t>
+          <t>Q2-T13</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3434.8</v>
+        <v>1455.8</v>
       </c>
     </row>
     <row r="19">
@@ -4652,18 +4652,18 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3466.7</v>
+        <v>1925.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Q2-T12,Q2-T21</t>
+          <t>Q2-T14</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3446.3</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="20">
@@ -4681,15 +4681,15 @@
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>4800.9</v>
+        <v>4129.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Q2-T07,Q2-T19</t>
+          <t>Q2-T07,Q2-T21</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4960.4</v>
+        <v>4192.9</v>
       </c>
     </row>
     <row r="21">
@@ -4707,15 +4707,15 @@
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>5016.7</v>
+        <v>4279.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Q2-T08,Q2-T18</t>
+          <t>Q2-T08,Q2-T19</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4700.5</v>
+        <v>4177.6</v>
       </c>
     </row>
     <row r="22">
@@ -4733,15 +4733,15 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2561.4</v>
+        <v>2413.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Q2-T13</t>
+          <t>Q2-T11</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2341.2</v>
+        <v>1997.3</v>
       </c>
     </row>
     <row r="23">
@@ -4759,15 +4759,15 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2375.4</v>
+        <v>2177</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Q2-T15</t>
+          <t>Q2-T12</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2075.4</v>
+        <v>2539.8</v>
       </c>
     </row>
   </sheetData>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>最低返航SOC 21.38%</t>
+          <t>最低返航SOC 20.69%</t>
         </is>
       </c>
     </row>
@@ -4922,10 +4922,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>66.85599999999999</v>
+        <v>64.459</v>
       </c>
       <c r="D2" t="n">
-        <v>7392.2</v>
+        <v>6522.3</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>71.83799999999999</v>
+        <v>67.306</v>
       </c>
       <c r="D3" t="n">
-        <v>6578</v>
+        <v>6279.1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -4972,10 +4972,10 @@
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>62.954</v>
+        <v>62.961</v>
       </c>
       <c r="D4" t="n">
-        <v>8457.9</v>
+        <v>7687.3</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -4997,10 +4997,10 @@
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>67.999</v>
+        <v>67.417</v>
       </c>
       <c r="D5" t="n">
-        <v>10309.1</v>
+        <v>9559.200000000001</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -5019,13 +5019,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>74.334</v>
+        <v>70.184</v>
       </c>
       <c r="D6" t="n">
-        <v>6542</v>
+        <v>6108.4</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
